--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="134">
   <si>
     <t>Sezione</t>
   </si>
@@ -119,6 +119,12 @@
     <t>descrizioneMotivoRecupero</t>
   </si>
   <si>
+    <t>Identificativo Atto Cartaceo</t>
+  </si>
+  <si>
+    <t>idAttoCartaceo</t>
+  </si>
+  <si>
     <t>Madre</t>
   </si>
   <si>
@@ -318,6 +324,12 @@
   </si>
   <si>
     <t>evento.intestatari[0]</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Atto collegato</t>
@@ -460,11 +472,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="22.48828125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="26.12109375" customWidth="true" bestFit="true"/>
@@ -750,62 +762,62 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>43</v>
@@ -814,12 +826,12 @@
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>44</v>
@@ -828,7 +840,7 @@
         <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>45</v>
@@ -837,12 +849,12 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>46</v>
@@ -851,7 +863,7 @@
         <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>47</v>
@@ -860,12 +872,12 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>48</v>
@@ -874,7 +886,7 @@
         <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>49</v>
@@ -883,12 +895,12 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>50</v>
@@ -897,7 +909,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>51</v>
@@ -906,12 +918,12 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>52</v>
@@ -920,7 +932,7 @@
         <v>25</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>53</v>
@@ -929,12 +941,12 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>
@@ -943,7 +955,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>55</v>
@@ -952,12 +964,12 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>56</v>
@@ -966,7 +978,7 @@
         <v>25</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>57</v>
@@ -975,12 +987,12 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>58</v>
@@ -989,7 +1001,7 @@
         <v>25</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>59</v>
@@ -998,12 +1010,12 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>60</v>
@@ -1012,7 +1024,7 @@
         <v>25</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>61</v>
@@ -1021,12 +1033,12 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>62</v>
@@ -1035,7 +1047,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>63</v>
@@ -1044,12 +1056,12 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>64</v>
@@ -1058,7 +1070,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>65</v>
@@ -1067,12 +1079,12 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>66</v>
@@ -1081,7 +1093,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>67</v>
@@ -1090,12 +1102,12 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>68</v>
@@ -1104,7 +1116,7 @@
         <v>25</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>69</v>
@@ -1113,12 +1125,12 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>70</v>
@@ -1127,7 +1139,7 @@
         <v>25</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>71</v>
@@ -1136,12 +1148,12 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>72</v>
@@ -1150,7 +1162,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>73</v>
@@ -1159,12 +1171,12 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>74</v>
@@ -1173,7 +1185,7 @@
         <v>25</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>75</v>
@@ -1182,12 +1194,12 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>76</v>
@@ -1196,7 +1208,7 @@
         <v>25</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>77</v>
@@ -1205,12 +1217,12 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>78</v>
@@ -1219,7 +1231,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>79</v>
@@ -1228,12 +1240,12 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>80</v>
@@ -1242,7 +1254,7 @@
         <v>25</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>81</v>
@@ -1251,12 +1263,12 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>82</v>
@@ -1265,7 +1277,7 @@
         <v>25</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>83</v>
@@ -1274,21 +1286,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>85</v>
@@ -1297,12 +1309,12 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>86</v>
@@ -1311,7 +1323,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>87</v>
@@ -1320,21 +1332,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>89</v>
@@ -1343,12 +1355,12 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
@@ -1357,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -1366,12 +1378,12 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
@@ -1380,7 +1392,7 @@
         <v>25</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>93</v>
@@ -1389,12 +1401,12 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
@@ -1403,7 +1415,7 @@
         <v>25</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>95</v>
@@ -1412,12 +1424,12 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
@@ -1426,7 +1438,7 @@
         <v>25</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>97</v>
@@ -1435,67 +1447,67 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>43</v>
@@ -1504,12 +1516,12 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>44</v>
@@ -1518,7 +1530,7 @@
         <v>25</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>45</v>
@@ -1527,12 +1539,12 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>46</v>
@@ -1541,7 +1553,7 @@
         <v>25</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>47</v>
@@ -1550,12 +1562,12 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>48</v>
@@ -1564,7 +1576,7 @@
         <v>25</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>49</v>
@@ -1573,12 +1585,12 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>50</v>
@@ -1587,7 +1599,7 @@
         <v>25</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>51</v>
@@ -1596,12 +1608,12 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>52</v>
@@ -1610,7 +1622,7 @@
         <v>25</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>53</v>
@@ -1619,12 +1631,12 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>54</v>
@@ -1633,7 +1645,7 @@
         <v>25</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>55</v>
@@ -1642,12 +1654,12 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>56</v>
@@ -1656,7 +1668,7 @@
         <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>57</v>
@@ -1665,12 +1677,12 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>58</v>
@@ -1679,7 +1691,7 @@
         <v>25</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>59</v>
@@ -1688,12 +1700,12 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>60</v>
@@ -1702,7 +1714,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>61</v>
@@ -1711,12 +1723,12 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>62</v>
@@ -1725,7 +1737,7 @@
         <v>25</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>63</v>
@@ -1734,12 +1746,12 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>64</v>
@@ -1748,7 +1760,7 @@
         <v>25</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>65</v>
@@ -1757,12 +1769,12 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>66</v>
@@ -1771,7 +1783,7 @@
         <v>25</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>67</v>
@@ -1780,12 +1792,12 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>68</v>
@@ -1794,7 +1806,7 @@
         <v>25</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>69</v>
@@ -1803,12 +1815,12 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>70</v>
@@ -1817,7 +1829,7 @@
         <v>25</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>71</v>
@@ -1826,12 +1838,12 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>72</v>
@@ -1840,7 +1852,7 @@
         <v>25</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>73</v>
@@ -1849,12 +1861,12 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>74</v>
@@ -1863,7 +1875,7 @@
         <v>25</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>75</v>
@@ -1872,12 +1884,12 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>76</v>
@@ -1886,7 +1898,7 @@
         <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>77</v>
@@ -1895,12 +1907,12 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>78</v>
@@ -1909,7 +1921,7 @@
         <v>25</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>79</v>
@@ -1918,12 +1930,12 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>80</v>
@@ -1932,7 +1944,7 @@
         <v>25</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>81</v>
@@ -1941,12 +1953,12 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>82</v>
@@ -1955,7 +1967,7 @@
         <v>25</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>83</v>
@@ -1964,21 +1976,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>85</v>
@@ -1987,12 +1999,12 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>86</v>
@@ -2001,7 +2013,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>87</v>
@@ -2010,21 +2022,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>89</v>
@@ -2033,12 +2045,12 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>90</v>
@@ -2047,7 +2059,7 @@
         <v>25</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>91</v>
@@ -2056,12 +2068,12 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>92</v>
@@ -2070,7 +2082,7 @@
         <v>25</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>93</v>
@@ -2079,12 +2091,12 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>94</v>
@@ -2093,7 +2105,7 @@
         <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>95</v>
@@ -2102,12 +2114,12 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>96</v>
@@ -2116,7 +2128,7 @@
         <v>25</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>97</v>
@@ -2125,7 +2137,7 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73">
@@ -2133,39 +2145,39 @@
         <v>100</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>101</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2176,16 +2188,16 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>43</v>
@@ -2199,16 +2211,16 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>45</v>
@@ -2222,7 +2234,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>46</v>
@@ -2231,7 +2243,7 @@
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>47</v>
@@ -2245,7 +2257,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>48</v>
@@ -2254,7 +2266,7 @@
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>49</v>
@@ -2268,7 +2280,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>50</v>
@@ -2277,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>51</v>
@@ -2291,16 +2303,16 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>53</v>
@@ -2314,7 +2326,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>54</v>
@@ -2323,7 +2335,7 @@
         <v>25</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>55</v>
@@ -2337,7 +2349,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>56</v>
@@ -2346,7 +2358,7 @@
         <v>25</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>57</v>
@@ -2360,7 +2372,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>58</v>
@@ -2369,7 +2381,7 @@
         <v>25</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>59</v>
@@ -2383,7 +2395,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>60</v>
@@ -2392,7 +2404,7 @@
         <v>25</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>61</v>
@@ -2406,7 +2418,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>62</v>
@@ -2415,7 +2427,7 @@
         <v>25</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>63</v>
@@ -2429,7 +2441,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>64</v>
@@ -2438,7 +2450,7 @@
         <v>25</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>65</v>
@@ -2452,7 +2464,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>66</v>
@@ -2461,7 +2473,7 @@
         <v>25</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>67</v>
@@ -2475,7 +2487,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>68</v>
@@ -2484,7 +2496,7 @@
         <v>25</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>69</v>
@@ -2498,7 +2510,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>70</v>
@@ -2507,7 +2519,7 @@
         <v>25</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>71</v>
@@ -2521,7 +2533,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>72</v>
@@ -2530,7 +2542,7 @@
         <v>25</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>73</v>
@@ -2544,7 +2556,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>74</v>
@@ -2553,7 +2565,7 @@
         <v>25</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>75</v>
@@ -2567,7 +2579,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>76</v>
@@ -2576,7 +2588,7 @@
         <v>25</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>77</v>
@@ -2590,7 +2602,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>78</v>
@@ -2599,7 +2611,7 @@
         <v>25</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>79</v>
@@ -2613,7 +2625,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>80</v>
@@ -2622,7 +2634,7 @@
         <v>25</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>81</v>
@@ -2636,7 +2648,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>82</v>
@@ -2645,7 +2657,7 @@
         <v>25</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>83</v>
@@ -2659,16 +2671,16 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>85</v>
@@ -2682,16 +2694,16 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>87</v>
@@ -2705,7 +2717,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>88</v>
@@ -2714,7 +2726,7 @@
         <v>25</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>89</v>
@@ -2728,7 +2740,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>90</v>
@@ -2737,7 +2749,7 @@
         <v>25</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>91</v>
@@ -2751,7 +2763,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>92</v>
@@ -2760,7 +2772,7 @@
         <v>25</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>93</v>
@@ -2774,7 +2786,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>94</v>
@@ -2783,7 +2795,7 @@
         <v>25</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>95</v>
@@ -2797,7 +2809,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>96</v>
@@ -2806,7 +2818,7 @@
         <v>25</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>97</v>
@@ -2823,22 +2835,22 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="E103" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104">
@@ -2846,36 +2858,36 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B105" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>109</v>
@@ -2884,12 +2896,12 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>110</v>
@@ -2898,7 +2910,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>111</v>
@@ -2907,12 +2919,12 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>112</v>
@@ -2921,7 +2933,7 @@
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>113</v>
@@ -2930,12 +2942,12 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>114</v>
@@ -2944,7 +2956,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>115</v>
@@ -2953,12 +2965,12 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>116</v>
@@ -2967,113 +2979,113 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>124</v>
@@ -3082,7 +3094,7 @@
         <v>25</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>125</v>
@@ -3091,12 +3103,12 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>126</v>
@@ -3105,7 +3117,7 @@
         <v>25</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>127</v>
@@ -3114,21 +3126,21 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>129</v>
@@ -3137,6 +3149,52 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_999.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="140">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,6 +35,18 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
@@ -44,9 +56,6 @@
     <t>SI</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Si puo' ignorare la sezione per</t>
   </si>
   <si>
@@ -87,9 +96,6 @@
   </si>
   <si>
     <t>Data decorrenza</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>dataDecorrenza</t>
@@ -484,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -543,63 +549,63 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -608,90 +614,90 @@
         <v>10</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>28</v>
@@ -700,21 +706,21 @@
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>30</v>
@@ -723,21 +729,21 @@
         <v>10</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -746,21 +752,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>34</v>
@@ -769,21 +775,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>36</v>
@@ -792,67 +798,67 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>45</v>
@@ -861,21 +867,21 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>47</v>
@@ -884,21 +890,21 @@
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>49</v>
@@ -907,21 +913,21 @@
         <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>51</v>
@@ -930,21 +936,21 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>53</v>
@@ -953,21 +959,21 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>55</v>
@@ -976,21 +982,21 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>57</v>
@@ -999,21 +1005,21 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>59</v>
@@ -1022,21 +1028,21 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>61</v>
@@ -1045,21 +1051,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>63</v>
@@ -1068,21 +1074,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>65</v>
@@ -1091,21 +1097,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>67</v>
@@ -1114,21 +1120,21 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>69</v>
@@ -1137,21 +1143,21 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>71</v>
@@ -1160,21 +1166,21 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>73</v>
@@ -1183,21 +1189,21 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>75</v>
@@ -1206,21 +1212,21 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>77</v>
@@ -1229,21 +1235,21 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>79</v>
@@ -1252,21 +1258,21 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>81</v>
@@ -1275,21 +1281,21 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>83</v>
@@ -1298,21 +1304,21 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>85</v>
@@ -1321,21 +1327,21 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>87</v>
@@ -1344,21 +1350,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>89</v>
@@ -1367,12 +1373,12 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>90</v>
@@ -1381,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>91</v>
@@ -1390,21 +1396,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>93</v>
@@ -1413,21 +1419,21 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>95</v>
@@ -1436,21 +1442,21 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>97</v>
@@ -1459,21 +1465,21 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>99</v>
@@ -1482,21 +1488,21 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>101</v>
@@ -1505,21 +1511,21 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>103</v>
@@ -1528,67 +1534,67 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="C46" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>45</v>
@@ -1597,21 +1603,21 @@
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>47</v>
@@ -1620,21 +1626,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>49</v>
@@ -1643,21 +1649,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>51</v>
@@ -1666,21 +1672,21 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>53</v>
@@ -1689,21 +1695,21 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>55</v>
@@ -1712,21 +1718,21 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>57</v>
@@ -1735,21 +1741,21 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>59</v>
@@ -1758,21 +1764,21 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>61</v>
@@ -1781,21 +1787,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>63</v>
@@ -1804,21 +1810,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>65</v>
@@ -1827,21 +1833,21 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>67</v>
@@ -1850,21 +1856,21 @@
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>69</v>
@@ -1873,21 +1879,21 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>71</v>
@@ -1896,21 +1902,21 @@
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>73</v>
@@ -1919,21 +1925,21 @@
         <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>75</v>
@@ -1942,21 +1948,21 @@
         <v>10</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>77</v>
@@ -1965,21 +1971,21 @@
         <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>79</v>
@@ -1988,21 +1994,21 @@
         <v>10</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>81</v>
@@ -2011,21 +2017,21 @@
         <v>10</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>83</v>
@@ -2034,21 +2040,21 @@
         <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>85</v>
@@ -2057,21 +2063,21 @@
         <v>10</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>87</v>
@@ -2080,21 +2086,21 @@
         <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>89</v>
@@ -2103,12 +2109,12 @@
         <v>10</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>90</v>
@@ -2117,7 +2123,7 @@
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>91</v>
@@ -2126,21 +2132,21 @@
         <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>93</v>
@@ -2149,21 +2155,21 @@
         <v>10</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>95</v>
@@ -2172,21 +2178,21 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>97</v>
@@ -2195,21 +2201,21 @@
         <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>99</v>
@@ -2218,21 +2224,21 @@
         <v>10</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>101</v>
@@ -2241,21 +2247,21 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>103</v>
@@ -2264,7 +2270,7 @@
         <v>10</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78">
@@ -2272,7 +2278,7 @@
         <v>106</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
@@ -2281,50 +2287,50 @@
         <v>107</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>45</v>
@@ -2333,12 +2339,12 @@
         <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>46</v>
@@ -2347,7 +2353,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>47</v>
@@ -2356,21 +2362,21 @@
         <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>49</v>
@@ -2379,21 +2385,21 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>51</v>
@@ -2402,12 +2408,12 @@
         <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>52</v>
@@ -2416,7 +2422,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>53</v>
@@ -2425,21 +2431,21 @@
         <v>10</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>55</v>
@@ -2448,21 +2454,21 @@
         <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>57</v>
@@ -2471,21 +2477,21 @@
         <v>10</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>59</v>
@@ -2494,21 +2500,21 @@
         <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>61</v>
@@ -2517,21 +2523,21 @@
         <v>10</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>63</v>
@@ -2540,21 +2546,21 @@
         <v>10</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>65</v>
@@ -2563,21 +2569,21 @@
         <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>67</v>
@@ -2586,21 +2592,21 @@
         <v>10</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>69</v>
@@ -2609,21 +2615,21 @@
         <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>71</v>
@@ -2632,21 +2638,21 @@
         <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>73</v>
@@ -2655,21 +2661,21 @@
         <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>75</v>
@@ -2678,21 +2684,21 @@
         <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>77</v>
@@ -2701,21 +2707,21 @@
         <v>10</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>79</v>
@@ -2724,21 +2730,21 @@
         <v>10</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>81</v>
@@ -2747,21 +2753,21 @@
         <v>10</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>83</v>
@@ -2770,21 +2776,21 @@
         <v>10</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>85</v>
@@ -2793,21 +2799,21 @@
         <v>10</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>87</v>
@@ -2816,21 +2822,21 @@
         <v>10</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>89</v>
@@ -2839,12 +2845,12 @@
         <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>90</v>
@@ -2853,7 +2859,7 @@
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>91</v>
@@ -2862,21 +2868,21 @@
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>93</v>
@@ -2885,21 +2891,21 @@
         <v>10</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>95</v>
@@ -2908,21 +2914,21 @@
         <v>10</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>97</v>
@@ -2931,21 +2937,21 @@
         <v>10</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>99</v>
@@ -2954,21 +2960,21 @@
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>101</v>
@@ -2977,21 +2983,21 @@
         <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>103</v>
@@ -3000,67 +3006,67 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B112" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>115</v>
@@ -3069,21 +3075,21 @@
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>117</v>
@@ -3092,21 +3098,21 @@
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>119</v>
@@ -3115,21 +3121,21 @@
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>121</v>
@@ -3138,21 +3144,21 @@
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>123</v>
@@ -3161,113 +3167,113 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>126</v>
+        <v>18</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>131</v>
@@ -3276,21 +3282,21 @@
         <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>133</v>
@@ -3299,21 +3305,21 @@
         <v>10</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>135</v>
@@ -3322,12 +3328,12 @@
         <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>136</v>
@@ -3336,7 +3342,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>137</v>
@@ -3345,7 +3351,30 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
